--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0136.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0136.xlsx
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Ồ... là vì ta chưa tiết kiệm đủ à? Ta có 140 Shell Credits đây... toàn bộ đây, lấy đi! À, mấy viên đá này với Arithmetic Shell nữa!</t>
+          <t>Ồ... là vì tao chưa tiết kiệm đủ à? Tao có 140 Shell Credits đây... toàn bộ đây, lấy đi! À, mấy viên đá này với Arithmetic Shell nữa!</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Nhưng mà... thực ra ta muốn nghe ý kiến cậu về một chuyện. Ý ta là tương lai của ta ấy.</t>
+          <t>Nhưng mà... thực ra tao muốn nghe ý kiến cậu về một chuyện. Ý tao là tương lai của tao ấy.</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Ừ, đúng là ta.</t>
+          <t>Ừ, đúng là tao.</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Ai thế? Còn {PlayerName} là ai? Ta không biết ngươi. Nhắn nhầm người rồi.</t>
+          <t>Ai thế? Còn {PlayerName} là ai? Tao không biết mày. Nhắn nhầm người rồi.</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Ừ, ta đây. Đoán là ngươi có tin gì rồi hả?</t>
+          <t>Ừ, tao đây. Đoán là mày có tin gì rồi hả?</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Còn nữa... có điều ta không đủ can đảm nói thẳng với ngươi, nên ta đành gõ ra đây thôi.</t>
+          <t>Còn nữa... có điều tao không đủ can đảm nói thẳng với mày, nên tao đành gõ ra đây thôi.</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Ta cứ nghĩ mãi, Void Storms đã biến mất, cơ hội tìm lại những gì mọi người đánh mất lại mong manh đến thế. Vậy thì làm để làm gì?</t>
+          <t>Tao cứ nghĩ mãi, Void Storms đã biến mất, cơ hội tìm lại những gì mọi người đánh mất lại mong manh đến thế. Vậy thì làm để làm gì?</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Ta không biết cậu đã gia nhập đội cứu hộ! Đúng người rồi! ...Nhưng mà, yêu cầu của ta khá bí mật đấy. Không sao chứ?</t>
+          <t>Tao không biết cậu đã gia nhập đội cứu hộ! Đúng người rồi! ...Nhưng mà, yêu cầu của tao khá bí mật đấy. Không sao chứ?</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Gì cơ?! Nhầm người à? Ta ghi sai thông tin liên lạc rồi... Ôi trời, xin lỗi vì kéo cậu vào vụ này. Nhưng thật lòng, cảm ơn cậu đã cứu ta!</t>
+          <t>Gì cơ?! Nhầm người à? Tao ghi sai thông tin liên lạc rồi... Ôi trời, xin lỗi vì kéo cậu vào vụ này. Nhưng thật lòng, cảm ơn cậu đã cứu tao!</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Ta đã nhắn tin đòi họ trả lời, mà họ lại chặn ta! Không thể để yên được.</t>
+          <t>Tao đã nhắn tin đòi họ trả lời, mà họ lại chặn tao! Không thể để yên được.</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Tính cả ta.</t>
+          <t>Tính cả tao.</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Đúng vậy! Nếu cậu không phiền, có thể cho bọn ta biết lý do cậu muốn lấy lại nó không?</t>
+          <t>Đúng vậy! Nếu cậu không phiền, có thể cho bọn tao biết lý do cậu muốn lấy lại nó không?</t>
         </is>
       </c>
     </row>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Gì cơ? Nếu cậu biết đó không phải của nó, sao cậu hứng thú lấy nó thế? Và sao cậu lại đeo cái giả này thay vì cái thật?</t>
+          <t>Gì cơ? Nếu mày biết đó không phải của nó, sao mày hứng thú lấy nó thế? Và sao mày lại đeo cái giả này thay vì cái thật?</t>
         </is>
       </c>
     </row>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Họ bảo cô ấy đã đi chệch hướng. Bảo cô ấy bị Bão Hư Không nuốt chửng. Hừ… cô ấy là người cẩn thận nhất mà ta từng biết. Không đời nào cô ấy lại…</t>
+          <t>Họ bảo cô ấy đã đi chệch hướng. Bảo cô ấy bị Bão Hư Không nuốt chửng. Hừ… cô ấy là người cẩn thận nhất mà tao từng biết. Không đời nào cô ấy lại…</t>
         </is>
       </c>
     </row>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Để tôi lo.</t>
+          <t>Để đó cho ta.</t>
         </is>
       </c>
     </row>
@@ -11429,7 +11429,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Sau đó ta leo lên đó và... ừm. Chả biết làm sao mà xuống được. Đành phải gọi người đến giúp.</t>
+          <t>Sau đó tao leo lên đó và... ừm. Chả biết làm sao mà xuống được. Đành phải gọi người đến giúp.</t>
         </is>
       </c>
     </row>
@@ -12729,7 +12729,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Haha! Thằng này chậm như rùa bò. Miếng sắt vụn cũ mèm mà bán cho nó xong, chúng ta ung dung bỏ túi 30,000 Shell Credits luôn.</t>
+          <t>Haha! Thằng này chậm như rùa bò. Miếng sắt vụn cũ mèm mà bán cho nó xong, chúng tao ung dung bỏ túi 30,000 Shell Credits luôn.</t>
         </is>
       </c>
     </row>
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Ta đoán họ đang gặp nhau bí mật... Chắc là bạn thân của nhau!</t>
+          <t>Tao đoán họ đang gặp nhau bí mật... Chắc là bạn thân của nhau!</t>
         </is>
       </c>
     </row>
@@ -14679,7 +14679,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Chụp ảnh là sở trường của ta. Được thôi.</t>
+          <t>Chụp ảnh là sở trường của tao. Được thôi.</t>
         </is>
       </c>
     </row>
@@ -16369,7 +16369,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Không vấn đề gì.</t>
+          <t>Không thành vấn đề.</t>
         </is>
       </c>
     </row>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Có phần thưởng không?</t>
+          <t>Có phần thưởng chứ?</t>
         </is>
       </c>
     </row>
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Ta không sao. Hoàn toàn không sao. Chỉ là... chẳng mầm nào sống sót cả. Haha...</t>
+          <t>Tao không sao. Hoàn toàn không sao. Chỉ là... chẳng mầm nào sống sót cả. Haha...</t>
         </is>
       </c>
     </row>
@@ -17994,7 +17994,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Chuyện gì đã xảy ra?</t>
+          <t>Chuyện gì đã xảy ra thế?</t>
         </is>
       </c>
     </row>
@@ -18254,7 +18254,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Ta chỉ muốn chứng minh với sư phụ rằng mình thực sự có tài năng cho việc này.</t>
+          <t>Tao chỉ muốn chứng minh với sư phụ rằng mình thực sự có tài năng cho việc này.</t>
         </is>
       </c>
     </row>
@@ -19164,7 +19164,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Bạn đang làm gì vậy?</t>
+          <t>Anh đang làm gì thế?</t>
         </is>
       </c>
     </row>
@@ -19229,7 +19229,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Ta tình cờ tìm thấy nơi này trong một chuyến thám hiểm. Đây là vị trí quan sát hoàn hảo. Từ đây, cậu có thể thấy toàn cảnh Dimmr Plains trải dài trước mắt.</t>
+          <t>Tao tình cờ tìm thấy nơi này trong một chuyến thám hiểm. Đây là vị trí quan sát hoàn hảo. Từ đây, cậu có thể thấy toàn cảnh Dimmr Plains trải dài trước mắt.</t>
         </is>
       </c>
     </row>
@@ -20724,7 +20724,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Ta cảm nhận được sự khác biệt ngay khi nó chạm đất. Hoàn toàn khác biệt!</t>
+          <t>Tao cảm nhận được sự khác biệt ngay khi nó chạm đất. Hoàn toàn khác biệt!</t>
         </is>
       </c>
     </row>
@@ -20789,7 +20789,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Ta đứng đó quan sát nó suốt mười lăm phút... Ở những lần khác, chúng đã héo úa từ lâu rồi.</t>
+          <t>Tao đứng đó quan sát nó suốt mười lăm phút... Ở những lần khác, chúng đã héo úa từ lâu rồi.</t>
         </is>
       </c>
     </row>
@@ -21179,7 +21179,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Cảm ơn {PlayerName}! Em sẽ ghi tên cậu vào báo cáo nghiên cứu mà em sắp nộp!</t>
+          <t>Cảm ơn {PlayerName}! Em sẽ ghi tên bạn vào báo cáo nghiên cứu mà em sắp nộp!</t>
         </is>
       </c>
     </row>
@@ -21439,7 +21439,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Chuyện gì đã xảy ra?</t>
+          <t>Chuyện gì đã xảy ra thế?</t>
         </is>
       </c>
     </row>
@@ -22219,7 +22219,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Làm sao đây? Ta có thật sự làm hỏng nó rồi không?</t>
+          <t>Làm sao đây? Tao có thật sự làm hỏng nó rồi không?</t>
         </is>
       </c>
     </row>
@@ -23259,7 +23259,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Ta nợ cậu một lần đấy! Không có thám tử này vác đồ, ta đã phải bỏ cuộc chuyến thám hiểm từ lâu rồi.</t>
+          <t>Tao nợ cậu một lần đấy! Không có thám tử này vác đồ, tao đã phải bỏ cuộc chuyến thám hiểm từ lâu rồi.</t>
         </is>
       </c>
     </row>
@@ -25599,7 +25599,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Ta đã gửi lời mời cho cậu ấy rồi. Ta mong sau khi tốt nghiệp, cậu ấy sẽ gia nhập nhóm nghiên cứu của ta tại Viện.</t>
+          <t>Tao đã gửi lời mời cho cậu ấy rồi. Tao mong sau khi tốt nghiệp, cậu ấy sẽ gia nhập nhóm nghiên cứu của tao tại Viện.</t>
         </is>
       </c>
     </row>
@@ -25924,7 +25924,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Chuyện gì đã xảy ra?</t>
+          <t>Chuyện gì đã xảy ra thế?</t>
         </is>
       </c>
     </row>
@@ -26314,7 +26314,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Ta không theo kịp rồi...</t>
+          <t>Tao không theo kịp rồi...</t>
         </is>
       </c>
     </row>
@@ -27224,7 +27224,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>ĐÚNG VẬY. Ngươi biến đi đâu rồi, Peep?! Không có ngươi, tương lai của đội ta còn tối tăm hơn cả Dimmr Plains…</t>
+          <t>ĐÚNG VẬY. Mày biến đi đâu rồi, Peep?! Không có mày, tương lai của đội ta còn tối tăm hơn cả Dimmr Plains…</t>
         </is>
       </c>
     </row>
@@ -28654,7 +28654,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Ta có linh cảm về chuyện này. Peep sẽ làm thay đổi tất cả những gì chúng ta biết về Kỹ thuật Mảng Ánh Sáng!</t>
+          <t>Tao có linh cảm về chuyện này. Peep sẽ làm thay đổi tất cả những gì chúng ta biết về Kỹ thuật Mảng Ánh Sáng!</t>
         </is>
       </c>
     </row>
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Việc đầu tiên ta làm sau khi ra viện là lao thẳng đến Hẻm Núi Fangspire.</t>
+          <t>Việc đầu tiên tao làm sau khi ra viện là lao thẳng đến Hẻm Núi Fangspire.</t>
         </is>
       </c>
     </row>
@@ -29759,7 +29759,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Khi đến nơi, ta đã dành cả ngày đi vòng quanh chỗ Bão Hư Không đánh trúng tụi mình.</t>
+          <t>Khi đến nơi, tao đã dành cả ngày đi vòng quanh chỗ Bão Hư Không đánh trúng tụi mình.</t>
         </is>
       </c>
     </row>
@@ -30019,7 +30019,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Và cái băng cát-sét nhỏ đó, ta chưa bao giờ đủ can đảm để nghe.</t>
+          <t>Và cái băng cát-sét nhỏ đó, tao chưa bao giờ đủ can đảm để nghe.</t>
         </is>
       </c>
     </row>
@@ -31059,7 +31059,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Rồi ta nghe thấy tiếng "Chạy đi!", tiếng bip bip từ Voidmatter Counter, rồi tiếng thở gấp của hắn khi đang chạy...</t>
+          <t>Rồi tao nghe thấy tiếng "Chạy đi!", tiếng bip bip từ Voidmatter Counter, rồi tiếng thở gấp của hắn khi đang chạy...</t>
         </is>
       </c>
     </row>
@@ -31579,7 +31579,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Lần sau gặp lại, {PlayerName}, ta sẽ không còn là đứa học trò núp sau lưng cậu nữa đâu.</t>
+          <t>Lần sau gặp lại, {PlayerName}, tao sẽ không còn là đứa học trò núp sau lưng cậu nữa đâu.</t>
         </is>
       </c>
     </row>
@@ -31709,7 +31709,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Ta muốn trở thành người như Nahum. Ta muốn cứu vớt bất cứ thứ gì có thể.</t>
+          <t>Tao muốn trở thành người như Nahum. Tao muốn cứu vớt bất cứ thứ gì có thể.</t>
         </is>
       </c>
     </row>
@@ -32879,7 +32879,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Dù bên trong là băng cassette của ta, nhưng giọng nói nghe được lại là của hắn, nghẹn ngào và xa xăm.</t>
+          <t>Dù bên trong là băng cassette của tao, nhưng giọng nói nghe được lại là của hắn, nghẹn ngào và xa xăm.</t>
         </is>
       </c>
     </row>
